--- a/naukri_jobs.xlsx
+++ b/naukri_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,14 +676,10 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>api developmentdebugbusiness requirementscloud platformsagile developmentbug fixingdockercloud</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3 weeks ago</t>
+          <t>Starts in 1-3 months</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -695,49 +691,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>python developer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>ewallsolutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chennai, Hyderabad, Bengaluru</t>
+          <t>Chennai, Madurai, Tiruppur, Salem, Tiruchirappalli, Coimbatore</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6-8 Yrs</t>
+          <t>0-3 Yrs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JavaPythonData ScienceDjangoPython DevelopmentScienceDevelopmentData</t>
+          <t>Computer scienceBasicVersion controlGITCodingDjangoProgrammingE-commerce</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1 week ago</t>
+          <t>3+ weeks ago</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-developer-tata-consultancy-services-hyderabad-chennai-bengaluru-6-to-8-years-260326016159</t>
+          <t>https://www.naukri.com/job-listings-python-developer-ewallsolutions-madurai-tiruppur-salem-chennai-tiruchirapalli-coimbatore-0-to-3-years-100725505184</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Python Developer - PET (Fresher)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Soul Ai</t>
+          <t>Regami Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -747,133 +743,133 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4-8 Yrs</t>
+          <t>0-1 Yrs</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PythonpandasdjangoAI modelsnumpyflaskjavascriptPython Development</t>
+          <t>Data Structures and AlgorithmsMongoDBMachine Learning &amp; Deep LearningMySQL DatabasePythonAI &amp; Data Science ConceptsLinux BasicsAPI Integration</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1 week ago</t>
+          <t>3+ weeks ago</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-developer-soul-ai-chennai-4-to-8-years-150926934061</t>
+          <t>https://www.naukri.com/job-listings-python-developer-pet-fresher-regami-solutions-chennai-0-to-1-years-250826024647</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Python Software Developer</t>
+          <t>ROS Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intellics Global Services</t>
+          <t>Ninos It Solution</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chennai, Hyderabad</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5-10 Yrs</t>
+          <t>0-2 Yrs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PythonDjangoFast APIAPIQuartzSQLFlaskSoftware development</t>
+          <t>c++pythoncloud servicesdevelopmentsoftware developmentsoftware testingverbal communicationmachine learning</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>3+ weeks ago</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-software-developer-intellics-global-services-hyderabad-chennai-5-to-10-years-220926029940</t>
+          <t>https://www.naukri.com/job-listings-ros-developer-ninos-it-solution-chennai-0-to-2-years-100726504728</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python Software Developer - Face To face</t>
+          <t>Required Java, Python, AI and App developer- Chennai</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Z Tech Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chennai, Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5-10 Yrs</t>
+          <t>0-1 Yrs</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWSMicroservicesPythonDjangoPython DevelopmentFlaskSoftware developmentDevelopment</t>
+          <t>JavaAi TechniquesArtificial Intelligence.NETPythonC++Fullstack DevelopmentFull Stack</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2 weeks ago</t>
+          <t>4 days ago</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-software-developer-face-to-face-hcltech-chennai-bengaluru-5-to-10-years-110726009961</t>
+          <t>https://www.naukri.com/job-listings-required-java-python-ai-and-app-developer-chennai-z-tech-solutions-chennai-0-to-1-years-250826018449</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Internship- Python Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xevyte Technologies</t>
+          <t>Viga Entertainment Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hybrid - Chennai, Hyderabad, Bengaluru</t>
+          <t>Chennai, Kolkata, Mumbai, New Delhi, Hyderabad, Pune, Bengaluru</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6-11 Yrs</t>
+          <t>0-1 Yrs</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Python DevelopmentNextjsNestjsDjangoPythonDevelopment</t>
+          <t>3D AnimatorSkill developmentCreative directionTime managementMayaAnimation3D animationInternship</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1 week ago</t>
+          <t>3+ weeks ago</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-developer-xevyte-technologies-hyderabad-chennai-bengaluru-6-to-11-years-100926020629</t>
+          <t>https://www.naukri.com/job-listings-internship-python-developer-viga-entertainment-technology-private-limited-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-0-to-1-years-300625501226</t>
         </is>
       </c>
     </row>
@@ -885,32 +881,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Limish</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hybrid - Chennai, Hyderabad, Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5-8 Yrs</t>
+          <t>0-1 Yrs</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>pythonNumpysqlPandasetlAutomationData EngineeringAPI Development</t>
+          <t>BackendDjangoAnalyticalDebuggingAutomation toolsProgrammingSQLPython</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1 week ago</t>
+          <t>3+ weeks ago</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-developer-infosys-hyderabad-chennai-bengaluru-5-to-8-years-150926036711</t>
+          <t>https://www.naukri.com/job-listings-python-developer-limish-chennai-0-to-1-years-130726502460</t>
         </is>
       </c>
     </row>
@@ -922,69 +918,69 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Tridots Tech</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hybrid - Chennai, Hyderabad, Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5-8 Yrs</t>
+          <t>0-2 Yrs</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>pythonNumpysqlPandasetlAutomationData EngineeringAPI Development</t>
+          <t>csspythondebugagile developmentbootstrappython developerweb applicationsjavascript</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1 week ago</t>
+          <t>2 weeks ago</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-developer-infosys-hyderabad-chennai-bengaluru-5-to-8-years-110926013782</t>
+          <t>https://www.naukri.com/job-listings-python-developer-tridots-tech-private-limited-chennai-0-to-2-years-080926501298</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Developer (5 To 8 Years)</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Saveetha Engineering College</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hybrid - Chennai, Hyderabad, Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5-8 Yrs</t>
+          <t>0-5 Yrs</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PythonGCPDjangoMySQLFast APIMicrosoft AzurePython DevelopmentAWS</t>
+          <t>emerging technologiespythonjavasoftware developmentversion controlagileagile developmentcommunication and interpersonal skills</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6 days ago</t>
+          <t>3+ weeks ago</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-developer-5-to-8-years-infosys-hyderabad-chennai-bengaluru-5-to-8-years-160926039006</t>
+          <t>https://www.naukri.com/job-listings-developer-saveetha-engineering-college-chennai-0-to-5-years-170826501489</t>
         </is>
       </c>
     </row>
@@ -996,81 +992,81 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>DLK Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chennai, Pune, Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4-8 Yrs</t>
+          <t>0-3 Yrs</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PandasPytestNumpyPythonData HandlingGithubPython DevelopmentHandling</t>
+          <t>servercssmicrosoft dynamics navisionnavisionsqlcalgitmicrosoft dynamics nav</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1 day ago</t>
+          <t>3+ weeks ago</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-developer-tata-consultancy-services-pune-chennai-bengaluru-4-to-8-years-210926001708</t>
+          <t>https://www.naukri.com/job-listings-python-developer-dlk-technologies-chennai-0-to-3-years-301025503045</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Python Developer | 3+ Years Experience</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TVM Infotech Private Limited</t>
+          <t>Alphaverse Consultants (opc)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chennai, Hyderabad, Bengaluru</t>
+          <t>Chennai(ECR)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3-8 Yrs</t>
+          <t>0-2 Yrs</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pythongenerative aiDjangoRest API ServicesAi PlatformFlaskSQLPython Development</t>
+          <t>PythonJavaEnglishHindiAWSTamilSQLSoftware engineering</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1 day ago</t>
+          <t>1 week ago</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-developer-3-years-experience-tvm-infotech-hyderabad-chennai-bengaluru-3-to-8-years-210926026375</t>
+          <t>https://www.naukri.com/job-listings-software-engineer-alphaverse-consultants-opc-chennai-0-to-2-years-140926001113</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Developer - Python</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kaspon</t>
+          <t>Tvm Infotech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1080,71 +1076,71 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5-7 Yrs</t>
+          <t>0-2 Yrs</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rest APIPythonDjangoPostgreSQLMySQLFast APIdatabase schemasMongoDB</t>
+          <t>cssc++androidajaxscalabilityjquerysqlcoding</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1 day ago</t>
+          <t>3+ weeks ago</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-software-developer-python-kaspontech-techworks-chennai-5-to-7-years-210926906964</t>
+          <t>https://www.naukri.com/job-listings-python-developer-tvminfotech-private-limited-chennai-0-to-2-years-170626501223</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Role For Python Developer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Altimetrik</t>
+          <t>Appzlogic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chennai, Pune, Bengaluru</t>
+          <t>Chennai, Kolkata, Mumbai, New Delhi, Hyderabad, Pune, Bengaluru</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6-9 Yrs</t>
+          <t>0-3 Yrs</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PysparkPythonDevelopment</t>
+          <t>pythoncsscsoftware testingnatural language processingpython developmentmachine learningartificial intelligence</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4 days ago</t>
+          <t>3+ weeks ago</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-role-for-python-developer-altimetrik-pune-chennai-bengaluru-6-to-9-years-180926019118</t>
+          <t>https://www.naukri.com/job-listings-python-developer-appzlogic-mobility-solutions-pvt-ltd-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-0-to-3-years-121124502854</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>SF Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Leading Client</t>
+          <t>Lorven Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1154,614 +1150,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6-10 Yrs</t>
+          <t>0-3 Yrs</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>python developerpythonPostgreSQLGitHubJSONHTTPSQL ServerGit</t>
+          <t>cssc++isodovhdljquerysqlapex</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6 days ago</t>
+          <t>3+ weeks ago</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-python-developer-purview-india-consulting-and-services-llp-chennai-6-to-10-years-160926923472</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Opportunities with HCLTech - DotNet Developer (Fresher)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Chennai, Bengaluru</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>0 Yrs</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>.NETC#ASP.NET.NET CoreCoreDotnet DevelopmentDevelopment</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2 weeks ago</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-opportunities-with-hcltech-dotnet-developer-fresher-hcltech-chennai-bengaluru-0-to-0-years-070926033659</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ewallsolutions</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Chennai, Madurai, Tiruppur, Salem, Tiruchirappalli, Coimbatore</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0-3 Yrs</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Computer scienceBasicVersion controlGITCodingDjangoProgrammingE-commerce</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-python-developer-ewallsolutions-madurai-tiruppur-salem-chennai-tiruchirapalli-coimbatore-0-to-3-years-100725505184</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Python Developer - PET (Fresher)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Regami Solutions</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0-1 Yrs</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Structures and AlgorithmsMongoDBMachine Learning &amp; Deep LearningMySQL DatabasePythonAI &amp; Data Science ConceptsLinux BasicsAPI Integration</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-python-developer-pet-fresher-regami-solutions-chennai-0-to-1-years-250826024647</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ROS Developer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Ninos It Solution</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>0-2 Yrs</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>c++pythoncloud servicesdevelopmentsoftware developmentsoftware testingverbal communicationmachine learning</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-ros-developer-ninos-it-solution-chennai-0-to-2-years-100726504728</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Required Java, Python, AI and App developer- Chennai</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Z Tech Solutions</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>0-1 Yrs</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>JavaAi TechniquesArtificial Intelligence.NETPythonC++Fullstack DevelopmentFull Stack</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>4 days ago</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-required-java-python-ai-and-app-developer-chennai-z-tech-solutions-chennai-0-to-1-years-250826018449</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Internship- Python Developer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Viga Entertainment Technology</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Chennai, Kolkata, Mumbai, New Delhi, Hyderabad, Pune, Bengaluru</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>0-1 Yrs</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>3D AnimatorSkill developmentCreative directionTime managementMayaAnimation3D animationInternship</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-internship-python-developer-viga-entertainment-technology-private-limited-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-0-to-1-years-300625501226</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Limish</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0-1 Yrs</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>BackendDjangoAnalyticalDebuggingAutomation toolsProgrammingSQLPython</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-python-developer-limish-chennai-0-to-1-years-130726502460</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Tridots Tech</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>0-2 Yrs</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>csspythondebugagile developmentbootstrappython developerweb applicationsjavascript</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2 weeks ago</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-python-developer-tridots-tech-private-limited-chennai-0-to-2-years-080926501298</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Saveetha Engineering College</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>0-5 Yrs</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>emerging technologiespythonjavasoftware developmentversion controlagileagile developmentcommunication and interpersonal skills</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-developer-saveetha-engineering-college-chennai-0-to-5-years-170826501489</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>DLK Technologies</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>0-3 Yrs</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>servercssmicrosoft dynamics navisionnavisionsqlcalgitmicrosoft dynamics nav</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-python-developer-dlk-technologies-chennai-0-to-3-years-301025503045</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>TVM Infotech Private Limited</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Chennai, Bengaluru</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>0 Yrs</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>JavaSpring BootManagement SkillsReact.jsAngularBootBootstrapFull Stack</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>6 days ago</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-java-full-stack-developer-tvm-infotech-chennai-bengaluru-0-to-0-years-160926010098</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Tvm Infotech</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>0-2 Yrs</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>cssc++androidajaxscalabilityjquerysqlcoding</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-python-developer-tvminfotech-private-limited-chennai-0-to-2-years-170626501223</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Appzlogic</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Chennai, Kolkata, Mumbai, New Delhi, Hyderabad, Pune, Bengaluru</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>0-3 Yrs</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>pythoncsscsoftware testingnatural language processingpython developmentmachine learningartificial intelligence</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-python-developer-appzlogic-mobility-solutions-pvt-ltd-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-0-to-3-years-121124502854</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Software-Java Developer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Creative Hands HR</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Chennai, Hyderabad, Bengaluru</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>0-5 Yrs</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>JavaRestful Web API DevelopmentMultithreadingDockerSpring BootCollectionsAWSMicroservices</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1 day ago</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-software-java-developer-creative-hands-hr-hyderabad-chennai-bengaluru-0-to-5-years-210926002974</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>SF Developer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Lorven Technologies</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>0-3 Yrs</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>cssc++isodovhdljquerysqlapex</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
           <t>https://www.naukri.com/job-listings-sf-developer-lorventech-solutions-india-pvt-ltd-chennai-0-to-3-years-090326502170</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Salesforce Vlocity Developer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Chennai, Gandhinagar, Gurugram</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>0-5 Yrs</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>SalesforceCssIntegrationArchitectureConfigurationCpqCustomizationHtml</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3 weeks ago</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-salesforce-vlocity-developer-capgemini-technology-services-india-limited-gandhinagar-chennai-gurugram-0-to-5-years-310826918596</t>
         </is>
       </c>
     </row>
